--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -360,7 +360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.453125" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="19.37" customWidth="1" style="4" min="1" max="1"/>
@@ -691,63 +691,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Pre-Test Functional</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Specific Impulse</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>isp</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>smart</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>pre test</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>post test</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
+    <row r="6" ht="15" customHeight="1" s="5"/>
     <row r="7" ht="15" customHeight="1" s="5"/>
     <row r="8" ht="15" customHeight="1" s="5"/>
     <row r="9" ht="15" customHeight="1" s="5"/>

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -655,7 +655,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Specific Impulse</t>
+          <t>Resistance</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>isp</t>
+          <t>resistance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -701,66 +701,9 @@
           <t>post test</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Resistance</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pre Test Functional</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>resistance</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>smart</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>pre test</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>post test</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>2</t>
         </is>

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -708,6 +708,43 @@
           <t>2</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ABPMPL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Pre Test Functional</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>full table</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -708,43 +708,6 @@
           <t>2</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ABPMPL</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Pre Test Functional</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>full table</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,6 +28,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="2">
@@ -50,9 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -421,12 +426,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -435,10 +440,15 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col hidden="1" width="14" customWidth="1" min="14" max="14"/>
+    <col hidden="1" width="14" customWidth="1" min="15" max="15"/>
+    <col hidden="1" width="14" customWidth="1" min="16" max="16"/>
+    <col hidden="1" width="14" customWidth="1" min="17" max="17"/>
+    <col hidden="1" width="14" customWidth="1" min="18" max="18"/>
+    <col hidden="1" width="14" customWidth="1" min="19" max="19"/>
+    <col hidden="1" width="14" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,271 +464,277 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Smart Snap Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GroupAfter</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>GroupBefore</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Range (min)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Range (max)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary Term</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Smart Position</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Anchor</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>FieldIndex</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>FieldSplit</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Range (min)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Range (max)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Format</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>GroupAfter</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>GroupBefore</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Smart Snap Type</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Secondary Term</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Smart Position</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>User-defined category for reporting/rollups</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Friendly label shown in outputs (leave blank to reuse Term)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Search term/anchor used by the scanner (required)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Page ranges (e.g., 1 or 2-4; comma/semicolon supported)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Fixed: smart</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Output type for value (number or string)</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Preferred units token(s) for numbers (pipe list ok)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Lower numeric bound (optional)</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Upper numeric bound (optional)</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Optional value mask (e.g., tpl-xxxx) or /regex/</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Only search after this anchor text (optional)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Stop searching once this anchor is reached (optional)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>auto|number|date|time|title (auto if blank)</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>Optional qualifier expected near the chosen value</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Pick the Nth value to the right (1-based) - overrides scoring</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Specific Impulse</t>
+          <t>Pre Test Functional</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Pre Test Functional</t>
+          <t>isp</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>isp</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pre Test</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Post Test</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
         <is>
           <t>number</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>pre test</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>post test</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Resistance</t>
+          <t>Pre Test Functional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pre Test Functional</t>
+          <t>resistance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>resistance</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pre Test</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Post Test</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>pre test</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>post test</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="E3:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"smart"</formula1>
+  <dataValidations count="4">
+    <dataValidation sqref="N2:N2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"smart,full table"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="T2:T2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"number,string"</formula1>
     </dataValidation>
-    <dataValidation sqref="M3:M2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"auto,number,date,time,title"</formula1>
+    <dataValidation sqref="S2:S2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"auto,groups,tokens"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>" ,auto,number,date,time,title"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -731,44 +747,181 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Smart Snap Terms Schema Template</t>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Smart-Snap Terms Schema</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>This template configures ONLY Smart Snap extraction. Columns are reduced to what Smart Snap needs.</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Fill rows in the Template sheet. Rows are processed in order using Smart-Snap extraction.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Data Group and Term Label are for reporting only—they flow to run outputs and the master workbook.</t>
-        </is>
-      </c>
+      <c r="A4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>For numbers, Units and Range help scoring; for strings/dates, set Return and Smart Snap Type.</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Required columns:</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Smart Position overrides scoring by selecting the Nth value to the right of the label.</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Term: The search term to find in the PDF (e.g., 'title', 'proof load', 'isp').</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Pages: One or more ranges (1-indexed). Examples: '1', '1-3', '5-7; 10; 12-13'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Data Organization:</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Data Group: Organize extracted data into categories (e.g., 'Metadata', 'Performance', 'Tables').</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Term Label: Friendly label for the extracted value in reports.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Search Configuration:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Smart Snap Type: Hint for extraction type - 'number', 'date', 'time', 'title', or blank for auto-detect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - GroupAfter / GroupBefore: Limit search to text appearing after/before these anchor terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Validation &amp; Scoring:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Units: Expected units (e.g., 'psi', 'sec', 'kg').</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Range (min) / Range (max): Valid range for numeric values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Format: Optional pattern or /regex/ for validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Advanced Extraction:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Secondary Term: Disambiguate values when multiple matches exist in a row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Smart Position: Position hint for value extraction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Tips:</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Leave columns blank when not needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Use consistent Data Groups and Term Labels to organize your dashboards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Save as .xlsx; the scanner also accepts .csv with the same column headers.</t>
         </is>
       </c>
     </row>

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -626,15 +626,19 @@
           <t>Post Test</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -664,7 +668,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>resistance</t>
+          <t>isp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +678,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>resistance</t>
+          <t>isp</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -692,8 +696,16 @@
           <t>Post Test</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -703,7 +715,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -717,6 +729,80 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pre Test Functional</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pre Test</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Post Test</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
         <is>
           <t>number</t>
         </is>

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Random Vib Z Amplitude</t>
+          <t>Thermal Soak High Duration</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Random Vib (Z)</t>
+          <t>Thermal Soak High</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1803,24 +1803,24 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>grms</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1842,12 +1842,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TC-02 Post Trim</t>
+          <t>Random Vib Z Amplitude</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>TC-02</t>
+          <t>Random Vib (Z)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1867,31 +1867,31 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>3. Environmental Endurance Matrix</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>5. Anomaly &amp; Waiver Log</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>grms</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Post</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>1</t>
@@ -1921,17 +1921,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LVDT-2 Status</t>
+          <t>TC-02 Post Trim</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LVDT-2</t>
+          <t>TC-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1949,28 +1949,28 @@
           <t>5. Anomaly &amp; Waiver Log</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>smart</t>
@@ -1982,6 +1982,80 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LVDT-2 Status</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LVDT-2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4. Calibration &amp; Trim Table</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5. Anomaly &amp; Waiver Log</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
         <is>
           <t>string</t>
         </is>

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -604,7 +604,11 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>smart</t>
@@ -639,7 +643,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Serial / component</t>
+          <t>Serial Component</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -674,7 +678,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>smart</t>
@@ -709,7 +717,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Date Compiled</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -732,7 +740,11 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>smart</t>
@@ -802,7 +814,11 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>smart</t>
@@ -1097,12 +1113,12 @@
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>smart</t>

--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -1,25 +1,59 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
+      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <family val="0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Cambria"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,123 +73,159 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDDDDDD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFDDDDDD"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -163,395 +233,245 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="130000"/>
+                <a:shade val="51000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:T22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:Q22"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="20.35" customWidth="1" style="4" min="1" max="1"/>
+    <col width="14" customWidth="1" style="4" min="2" max="2"/>
+    <col width="17" customWidth="1" style="4" min="3" max="3"/>
+    <col width="17.29" customWidth="1" style="4" min="4" max="4"/>
+    <col width="16" customWidth="1" style="4" min="5" max="5"/>
+    <col width="14" customWidth="1" style="4" min="6" max="12"/>
+    <col width="16" customWidth="1" style="4" min="13" max="13"/>
+    <col width="14" customWidth="1" style="4" min="14" max="15"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="5">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Data Group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Term Label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Smart Snap Type</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Secondary Term</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>GroupAfter</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>GroupBefore</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Range (min)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Range (max)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Secondary Term</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Smart Position</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
+        <is>
+          <t>OCR_Row_EPS</t>
+        </is>
+      </c>
+      <c r="O1" s="6" t="inlineStr">
+        <is>
+          <t>DPI</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Anchor</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>FieldIndex</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>FieldSplit</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="15" customHeight="1" s="5">
       <c r="A2" t="inlineStr">
         <is>
           <t>Document Profile</t>
@@ -572,26 +492,22 @@
           <t>Program</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Field Value</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -602,30 +518,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="15" customHeight="1" s="5">
       <c r="A3" t="inlineStr">
         <is>
           <t>Document Profile</t>
@@ -643,29 +560,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Serial Component</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+          <t>Serial</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Field Value</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -676,132 +589,118 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="5">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Document Profile</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Date Compiled</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>smart</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Document Profile</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Date Compiled</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Field Value</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Document Profile</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Source Bundle Path</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Source Bundle</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>smart</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Document Profile</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Source Bundle Path</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Source Bundle</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Field Value</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -812,30 +711,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1" s="5">
       <c r="A6" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -858,58 +758,55 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>psia</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>195</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Measured</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1" s="5">
       <c r="A7" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -930,26 +827,22 @@
           <t>chamber_pressure</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -960,30 +853,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1" s="5">
       <c r="A8" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -1006,62 +900,59 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Ohm</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Measured</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1" s="5">
       <c r="A9" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -1084,24 +975,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>1. Functional Acceptance Snapshot</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1112,30 +1003,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Data Quality</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1" s="5">
       <c r="A10" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1156,56 +1048,53 @@
           <t>thrust_nominal</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1" s="5">
       <c r="A11" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1228,54 +1117,51 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="15" customHeight="1" s="5">
       <c r="A12" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1298,54 +1184,51 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1" s="5">
       <c r="A13" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1368,54 +1251,51 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>155</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1" s="5">
       <c r="A14" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1436,26 +1316,22 @@
           <t>power_draw_peak</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1466,26 +1342,27 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1" s="5">
       <c r="A15" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1506,26 +1383,22 @@
           <t>power_draw_idle</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1536,26 +1409,27 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1" s="5">
       <c r="A16" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1578,24 +1452,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>2. Performance KPI Table</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1606,30 +1480,27 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1" s="5">
       <c r="A17" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1652,24 +1523,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>Requirement Met?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1680,34 +1551,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Requirement Met?</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1" s="5">
       <c r="A18" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1728,26 +1596,22 @@
           <t>Thermal Soak High</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1758,30 +1622,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1" s="5">
       <c r="A19" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1802,26 +1667,22 @@
           <t>Thermal Soak High</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1832,30 +1693,31 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1" s="5">
       <c r="A20" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1876,60 +1738,57 @@
           <t>Random Vib (Z)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>3. Environmental Endurance Matrix</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>grms</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1" s="5">
       <c r="A21" t="inlineStr">
         <is>
           <t>Calibration</t>
@@ -1952,58 +1811,55 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>5. Anomaly &amp; Waiver Log</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>1.01</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Post</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1" s="5">
       <c r="A22" t="inlineStr">
         <is>
           <t>Calibration</t>
@@ -2026,24 +1882,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>4. Calibration &amp; Trim Table</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>5. Anomaly &amp; Waiver Log</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2054,198 +1910,259 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="I3:I2000 J3:J2000 K3:K2000">
+    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+      <formula>$C3="title"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C23:C1022" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+      <formula1>",auto,number,date,time,title"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="0">
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A33"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="110" customWidth="1" style="4" min="1" max="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="16.15" customHeight="1" s="5">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Smart-Snap Terms Schema</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="15" customHeight="1" s="5">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Fill rows in the Template sheet. Rows are processed in order using Smart-Snap extraction.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="4" ht="15" customHeight="1" s="5">
+      <c r="A4" s="8" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="5">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Required columns:</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="15" customHeight="1" s="5">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Term: The search term to find in the PDF (e.g., 'title', 'proof load', 'isp').</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="15" customHeight="1" s="5">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Pages: One or more ranges (1-indexed). Examples: '1', '1-3', '5-7; 10; 12-13'.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="5">
+      <c r="A8" s="8" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="5">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Data Organization:</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="15" customHeight="1" s="5">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Data Group: Organize extracted data into categories (e.g., 'Metadata', 'Performance', 'Tables').</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="15" customHeight="1" s="5">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Term Label: Friendly label for the extracted value in reports.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12" ht="15" customHeight="1" s="5">
+      <c r="A12" s="8" t="n"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="5">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Search Configuration:</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="15" customHeight="1" s="5">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Smart Snap Type: Hint for extraction type - 'number', 'date', 'time', 'title', or blank for auto-detect.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="15" ht="15" customHeight="1" s="5">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - GroupAfter / GroupBefore: Limit search to text appearing after/before these anchor terms.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="16" ht="15" customHeight="1" s="5">
+      <c r="A16" s="8" t="n"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="5">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Validation &amp; Scoring:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="5">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Units: Expected units (e.g., 'psi', 'sec', 'kg').</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19" ht="15" customHeight="1" s="5">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Range (min) / Range (max): Valid range for numeric values.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="20" ht="15" customHeight="1" s="5">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Format: Optional pattern or /regex/ for validation.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21" ht="15" customHeight="1" s="5">
+      <c r="A21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="5">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Advanced Extraction:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="23" ht="15" customHeight="1" s="5">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Secondary Term: Disambiguate values when multiple matches exist in a row.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24" ht="15" customHeight="1" s="5">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Smart Position: Position hint for value extraction.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="5">
+      <c r="A25" s="8" t="n"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="5">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>OCR Fine-Tuning (optional):</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="5">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - OCR_Row_EPS: Y-axis tolerance (0.5-50.0) for grouping OCR text into rows. Default: 8.0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="5">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - DPI: OCR rendering resolution (e.g., 700, 850). Higher values improve accuracy for small text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="5">
+      <c r="A29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="5">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Tips:</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="31" ht="15" customHeight="1" s="5">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Leave columns blank when not needed.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="32" ht="15" customHeight="1" s="5">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Use consistent Data Groups and Term Labels to organize your dashboards.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="33" ht="15" customHeight="1" s="5">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Save as .xlsx; the scanner also accepts .csv with the same column headers.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -1,59 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Template" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Cambria"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -73,159 +39,124 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDDDDD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFDDDDDD"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -233,245 +164,385 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="20.35" customWidth="1" style="4" min="1" max="1"/>
-    <col width="14" customWidth="1" style="4" min="2" max="2"/>
-    <col width="17" customWidth="1" style="4" min="3" max="3"/>
-    <col width="17.29" customWidth="1" style="4" min="4" max="4"/>
-    <col width="16" customWidth="1" style="4" min="5" max="5"/>
-    <col width="14" customWidth="1" style="4" min="6" max="12"/>
-    <col width="16" customWidth="1" style="4" min="13" max="13"/>
-    <col width="14" customWidth="1" style="4" min="14" max="15"/>
-  </cols>
+  <dimension ref="A1:R22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="5">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Data Group</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Term Label</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Smart Snap Type</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Term</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Secondary Term</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Pages</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GroupAfter</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GroupBefore</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Range (min)</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Range (max)</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="M1" s="6" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Alt Search</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>Smart Position</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>OCR_Row_EPS</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>DPI</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Return</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="5">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>Document Profile</t>
@@ -500,12 +571,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Field Value</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>ignition_delay</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -524,25 +595,31 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Document Profile</t>
@@ -571,12 +648,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Field Value</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>ignition_delay</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,19 +674,25 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>Document Profile</t>
@@ -638,12 +721,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Field Value</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>ignition_delay</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -652,19 +735,25 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="5">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>Document Profile</t>
@@ -693,12 +782,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Field Value</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>thrust_nominal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -717,25 +806,31 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -768,12 +863,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>Source Bundle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>thrust_nominal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -783,30 +878,40 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>below</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -835,12 +940,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>Source Bundle</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>thrust_nominal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -859,25 +964,31 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>Functional Acceptance</t>
@@ -905,92 +1016,98 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thermal Soak Low</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Ohm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>5.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Functional Acceptance</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Harness Resistance Quality</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>resistance</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Quality</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1. Functional Acceptance Snapshot</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2. Performance KPI Table</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Ohm</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4.8</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>5.3</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>smart</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="5">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Functional Acceptance</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Harness Resistance Quality</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>resistance</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Quality</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>1-4</t>
-        </is>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1. Functional Acceptance Snapshot</t>
+          <t>Source Bundle</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>thrust_nominal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1010,24 +1127,25 @@
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1056,12 +1174,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>leak_check</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1076,25 +1194,31 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1127,12 +1251,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>thermal_margin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1149,19 +1273,25 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1194,12 +1324,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>leak_check</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1216,19 +1346,25 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="5">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1261,12 +1397,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>leak_check</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1283,19 +1419,25 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1319,17 +1461,17 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>leak_check</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1350,19 +1492,25 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1386,17 +1534,17 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>leak_check</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1417,19 +1565,25 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>Performance KPI</t>
@@ -1462,12 +1616,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2. Performance KPI Table</t>
+          <t>leak_check</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1488,19 +1642,25 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="5">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1533,12 +1693,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>thermal_margin</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4. Calibration &amp; Trim Table</t>
+          <t>Thermal Soak Low</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1557,25 +1717,31 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1604,12 +1770,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>thermal_margin</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4. Calibration &amp; Trim Table</t>
+          <t>TC-01</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1628,25 +1794,31 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1675,12 +1847,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>thermal_margin</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4. Calibration &amp; Trim Table</t>
+          <t>TC-01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1699,25 +1871,31 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Environmental</t>
@@ -1746,12 +1924,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3. Environmental Endurance Matrix</t>
+          <t>thermal_margin</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4. Calibration &amp; Trim Table</t>
+          <t>TC-01</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1770,25 +1948,31 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="5">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>Calibration</t>
@@ -1821,15 +2005,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4. Calibration &amp; Trim Table</t>
+          <t>Sine Sweep</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5. Anomaly &amp; Waiver Log</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>0.99</t>
@@ -1841,25 +2029,31 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>
+</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="5">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>Calibration</t>
@@ -1892,12 +2086,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4. Calibration &amp; Trim Table</t>
+          <t>Sine Sweep</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5. Anomaly &amp; Waiver Log</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1917,252 +2111,221 @@
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>smart</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I3:I2000 J3:J2000 K3:K2000">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>$C3="title"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="C23:C1022" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>",auto,number,date,time,title"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="1" zeroHeight="0" outlineLevelRow="0"/>
-  <cols>
-    <col width="110" customWidth="1" style="4" min="1" max="1"/>
-  </cols>
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="16.15" customHeight="1" s="5">
-      <c r="A1" s="7" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Smart-Snap Terms Schema</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="5">
-      <c r="A3" s="8" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Fill rows in the Template sheet. Rows are processed in order using Smart-Snap extraction.</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="5">
-      <c r="A4" s="8" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="5">
-      <c r="A5" s="8" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Required columns:</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="5">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Term: The search term to find in the PDF (e.g., 'title', 'proof load', 'isp').</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="5">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Pages: One or more ranges (1-indexed). Examples: '1', '1-3', '5-7; 10; 12-13'.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="5">
-      <c r="A8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="5">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Data Organization:</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="5">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Data Group: Organize extracted data into categories (e.g., 'Metadata', 'Performance', 'Tables').</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="5">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Term Label: Friendly label for the extracted value in reports.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="5">
-      <c r="A12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="5">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Search Configuration:</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="5">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Smart Snap Type: Hint for extraction type - 'number', 'date', 'time', 'title', or blank for auto-detect.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="5">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t xml:space="preserve"> - GroupAfter / GroupBefore: Limit search to text appearing after/before these anchor terms.</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="5">
-      <c r="A16" s="8" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="5">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Alt Search: Optional vertical search direction for numeric Smart Snap terms — 'below' or 'above'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Validation &amp; Scoring:</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="5">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Units: Expected units (e.g., 'psi', 'sec', 'kg').</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="5">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Range (min) / Range (max): Valid range for numeric values.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="5">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Format: Optional pattern or /regex/ for validation.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="5">
-      <c r="A21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="5">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Advanced Extraction:</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="5">
-      <c r="A23" s="8" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Secondary Term: Disambiguate values when multiple matches exist in a row.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="5">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Smart Position: Position hint for value extraction.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="5">
-      <c r="A25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="5">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>OCR Fine-Tuning (optional):</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="5">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t xml:space="preserve"> - OCR_Row_EPS: Y-axis tolerance (0.5-50.0) for grouping OCR text into rows. Default: 8.0.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="5">
-      <c r="A28" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t xml:space="preserve"> - DPI: OCR rendering resolution (e.g., 700, 850). Higher values improve accuracy for small text.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="5">
-      <c r="A29" s="8" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="5">
-      <c r="A30" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Tips:</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="5">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Leave columns blank when not needed.</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="5">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Use consistent Data Groups and Term Labels to organize your dashboards.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="5">
-      <c r="A33" s="8" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Save as .xlsx; the scanner also accepts .csv with the same column headers.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/user_inputs/terms.schema.smartsnap.xlsx
+++ b/user_inputs/terms.schema.smartsnap.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R22"/>
+  <dimension ref="A1:R23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,6 +2124,82 @@
         </is>
       </c>
       <c r="R22" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Calibration</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LVDT-2 Pre Trim</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LVDT-2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sine Sweep</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>smart</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
         <is>
           <t>string</t>
         </is>
